--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488006_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488006_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.8801</v>
+        <v>5.2491</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0792</v>
+        <v>5.5886</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1991</v>
+        <v>-0.3395</v>
       </c>
       <c r="G2" t="n">
         <v>4.3992</v>
@@ -610,13 +610,13 @@
         <v>2.1805</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1912</v>
+        <v>-0.8223</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8184</v>
+        <v>-0.3091</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.3728</v>
+        <v>-0.5132</v>
       </c>
       <c r="V2" t="n">
         <v>0.4828</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>V. STRUKOV STRUKOV</t>
+          <t>A. GONZALEZ PEREZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0815</v>
+        <v>-1.1073</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0798</v>
+        <v>0.3389</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.1612</v>
+        <v>-1.4462</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.4586</v>
+        <v>-2.7234</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2328</v>
+        <v>0.2707</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6914</v>
+        <v>-2.9941</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2779</v>
+        <v>-1.1046</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2377</v>
+        <v>1.5277</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0402</v>
+        <v>-2.6323</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.7365</v>
+        <v>-1.6189</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.005</v>
+        <v>-1.257</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.7315</v>
+        <v>-0.3619</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1982</v>
+        <v>0.9911</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9911</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1982</v>
+        <v>1.9822</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8528</v>
+        <v>-1.8143</v>
       </c>
       <c r="T4" t="n">
-        <v>1.4758</v>
+        <v>-0.5128</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.623</v>
+        <v>-1.3016</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.674</v>
+        <v>2.4394</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.674</v>
+        <v>2.9474</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.508</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GONZALEZ PEREZ</t>
+          <t>A. GARCIA MONTELLANO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2444</v>
+        <v>-1.265</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0333</v>
+        <v>0.1145</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.2777</v>
+        <v>-1.3795</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.7234</v>
+        <v>0.8349</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2707</v>
+        <v>0.1117</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.9941</v>
+        <v>0.7232</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.1046</v>
+        <v>1.8149</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5277</v>
+        <v>1.2447</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.6323</v>
+        <v>0.5703</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6189</v>
+        <v>-0.98</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.257</v>
+        <v>-1.1329</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3619</v>
+        <v>0.1529</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9911</v>
+        <v>-0.1982</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R5" t="n">
-        <v>1.9822</v>
+        <v>0.7929</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.9515</v>
+        <v>-1.0315</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8184</v>
+        <v>-0.7093</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.1331</v>
+        <v>-0.3222</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4394</v>
+        <v>-0.8701</v>
       </c>
       <c r="W5" t="n">
-        <v>2.9474</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.508</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.2708</v>
+        <v>-1.436</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.1089</v>
+        <v>-2.4145</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8381</v>
+        <v>0.9785</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6107</v>
@@ -922,13 +922,13 @@
         <v>0.9911</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3432</v>
+        <v>-0.5084</v>
       </c>
       <c r="T6" t="n">
-        <v>0.18</v>
+        <v>-0.1257</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5231</v>
+        <v>-0.3827</v>
       </c>
       <c r="V6" t="n">
         <v>-0.3169</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GARCIA MONTELLANO</t>
+          <t>O. GARCIA JIMENEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.4511</v>
+        <v>-1.8117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0126</v>
+        <v>-0.5819</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4637</v>
+        <v>-1.2298</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8349</v>
+        <v>-1.6658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1117</v>
+        <v>-1.2697</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7232</v>
+        <v>-0.3961</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8149</v>
+        <v>-0.5984</v>
       </c>
       <c r="K7" t="n">
-        <v>1.2447</v>
+        <v>-0.5984</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5703</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.98</v>
+        <v>-1.0674</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.1329</v>
+        <v>-0.6713</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1529</v>
+        <v>-0.3961</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1982</v>
+        <v>0.1982</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7929</v>
+        <v>0.1982</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.2176</v>
+        <v>-0.3441</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8112</v>
+        <v>0.0165</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4065</v>
+        <v>-0.3607</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. LALI VICENTE UCHUATE</t>
+          <t>V. STRUKOV STRUKOV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0232</v>
+        <v>-2.1178</v>
       </c>
       <c r="E8" t="n">
-        <v>1.9369</v>
+        <v>0.9592000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.9601</v>
+        <v>-3.077</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0928</v>
+        <v>-1.4586</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3671</v>
+        <v>0.2328</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4599</v>
+        <v>-1.6914</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0227</v>
+        <v>1.2779</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7018</v>
+        <v>1.2377</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6791</v>
+        <v>0.0402</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.1155</v>
+        <v>-2.7365</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.3347</v>
+        <v>-1.005</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7806999999999999</v>
+        <v>-1.7315</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5858</v>
+        <v>0.1982</v>
       </c>
       <c r="S8" t="n">
-        <v>0.743</v>
+        <v>-0.1835</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9142</v>
+        <v>0.3553</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1713</v>
+        <v>-0.5387</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.2592</v>
+        <v>-0.674</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.674</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.2592</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. GARCIA JIMENEZ</t>
+          <t>P. BILEISIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0435</v>
+        <v>-2.3863</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7856</v>
+        <v>-3.62</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.2579</v>
+        <v>1.2336</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6658</v>
+        <v>-2.1698</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2697</v>
+        <v>0.2982</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3961</v>
+        <v>-2.4679</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5984</v>
+        <v>-1.4938</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5984</v>
+        <v>0.6122</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-2.1061</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0674</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.6713</v>
+        <v>-0.3141</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3961</v>
+        <v>-0.3619</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1982</v>
+        <v>0.3964</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1982</v>
+        <v>2.3787</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.576</v>
+        <v>-1.6491</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1872</v>
+        <v>-0.6771</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3888</v>
+        <v>-0.9721</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.0361</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5331</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.5029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. BILEISIS</t>
+          <t>A. LOPEZ MENACHO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.899</v>
+        <v>-2.7106</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.8237</v>
+        <v>-2.6693</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9248</v>
+        <v>-0.0413</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1698</v>
+        <v>-1.8604</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2982</v>
+        <v>-1.0625</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.4679</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.4938</v>
+        <v>-1.0083</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6122</v>
+        <v>-0.3292</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.1061</v>
+        <v>-0.6791</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6758999999999999</v>
+        <v>-0.852</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.3141</v>
+        <v>-0.7333</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3619</v>
+        <v>-0.1187</v>
       </c>
       <c r="P10" t="n">
-        <v>0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9822</v>
+        <v>-0.9911</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3787</v>
+        <v>1.1893</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.1617</v>
+        <v>-0.9278</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8808</v>
+        <v>-0.6698</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2809</v>
+        <v>-0.2579</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0361</v>
+        <v>-0.1207</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5331</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5029</v>
+        <v>-0.1207</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. LOPEZ MENACHO</t>
+          <t>E. LALI VICENTE UCHUATE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9424</v>
+        <v>-3.2874</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.873</v>
+        <v>1.122</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0694</v>
+        <v>-4.4094</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.8604</v>
+        <v>-1.0928</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.0625</v>
+        <v>0.3671</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-1.4599</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0083</v>
+        <v>1.0227</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3292</v>
+        <v>1.7018</v>
       </c>
       <c r="L11" t="n">
         <v>-0.6791</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.852</v>
+        <v>-2.1155</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7333</v>
+        <v>-1.3347</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1187</v>
+        <v>-0.7806999999999999</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1982</v>
+        <v>1.5858</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9911</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1893</v>
+        <v>1.5858</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1596</v>
+        <v>-0.5212</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8736</v>
+        <v>0.0993</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.286</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.1207</v>
+        <v>-3.2592</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.1207</v>
+        <v>-3.2592</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7102</v>
+        <v>-3.9129</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3844</v>
+        <v>-3.6713</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3258</v>
+        <v>-0.2416</v>
       </c>
       <c r="G12" t="n">
         <v>-2.9028</v>
@@ -1390,13 +1390,13 @@
         <v>1.1893</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8344</v>
+        <v>-1.0371</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0608</v>
+        <v>-0.3477</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7736</v>
+        <v>-0.6894</v>
       </c>
       <c r="V12" t="n">
         <v>0.8198</v>
@@ -1423,19 +1423,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.3996</v>
+        <v>-14.3995</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.1684</v>
+        <v>-5.168399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.231</v>
+        <v>-9.231199999999999</v>
       </c>
       <c r="G13" t="n">
         <v>-7.668499999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.705800000000001</v>
+        <v>3.7058</v>
       </c>
       <c r="I13" t="n">
         <v>-11.3742</v>
@@ -1468,13 +1468,13 @@
         <v>12.8844</v>
       </c>
       <c r="S13" t="n">
-        <v>-8.975199999999999</v>
+        <v>-8.975100000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.1924</v>
+        <v>-3.192400000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-5.7829</v>
+        <v>-5.7828</v>
       </c>
       <c r="V13" t="n">
         <v>-0.7293999999999999</v>
@@ -1483,7 +1483,7 @@
         <v>4.2098</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.9393</v>
+        <v>-4.939299999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.3043</v>
+        <v>7.7146</v>
       </c>
       <c r="E14" t="n">
         <v>6.9205</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3838</v>
+        <v>0.7941</v>
       </c>
       <c r="G14" t="n">
         <v>4.3819</v>
@@ -1546,13 +1546,13 @@
         <v>0.5947</v>
       </c>
       <c r="S14" t="n">
-        <v>2.191</v>
+        <v>1.6014</v>
       </c>
       <c r="T14" t="n">
         <v>0.3599</v>
       </c>
       <c r="U14" t="n">
-        <v>1.8311</v>
+        <v>1.2415</v>
       </c>
       <c r="V14" t="n">
         <v>1.1367</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. PALOMO GIL</t>
+          <t>T. PARRA MENDIVIL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.7848</v>
+        <v>5.4823</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3918</v>
+        <v>3.3754</v>
       </c>
       <c r="F15" t="n">
-        <v>2.393</v>
+        <v>2.1069</v>
       </c>
       <c r="G15" t="n">
-        <v>1.7959</v>
+        <v>5.0168</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1554</v>
+        <v>-0.0015</v>
       </c>
       <c r="I15" t="n">
-        <v>1.9513</v>
+        <v>5.0183</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0875</v>
+        <v>4.1241</v>
       </c>
       <c r="K15" t="n">
-        <v>1.0434</v>
+        <v>0.4641</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0441</v>
+        <v>3.6601</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7084</v>
+        <v>0.8927</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1989</v>
+        <v>-0.4656</v>
       </c>
       <c r="O15" t="n">
-        <v>1.9073</v>
+        <v>1.3583</v>
       </c>
       <c r="P15" t="n">
-        <v>0.1982</v>
+        <v>-0.3964</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1893</v>
+        <v>0.5947</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7135</v>
+        <v>1.0581</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2886</v>
+        <v>0.2423</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4249</v>
+        <v>0.8157</v>
       </c>
       <c r="V15" t="n">
-        <v>2.0772</v>
+        <v>-0.1962</v>
       </c>
       <c r="W15" t="n">
-        <v>2.0068</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0704</v>
+        <v>-0.1962</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T. PARRA MENDIVIL</t>
+          <t>V. PALOMO GIL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.2857</v>
+        <v>5.2441</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3754</v>
+        <v>3.1881</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9104</v>
+        <v>2.056</v>
       </c>
       <c r="G16" t="n">
-        <v>5.0168</v>
+        <v>1.7959</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0015</v>
+        <v>-0.1554</v>
       </c>
       <c r="I16" t="n">
-        <v>5.0183</v>
+        <v>1.9513</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1241</v>
+        <v>1.0875</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4641</v>
+        <v>1.0434</v>
       </c>
       <c r="L16" t="n">
-        <v>3.6601</v>
+        <v>0.0441</v>
       </c>
       <c r="M16" t="n">
-        <v>0.8927</v>
+        <v>0.7084</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4656</v>
+        <v>-1.1989</v>
       </c>
       <c r="O16" t="n">
-        <v>1.3583</v>
+        <v>1.9073</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.3964</v>
+        <v>0.1982</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.9911</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5947</v>
+        <v>1.1893</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8615</v>
+        <v>1.1728</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2423</v>
+        <v>1.0849</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6192</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.1962</v>
+        <v>2.0772</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.0068</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1962</v>
+        <v>0.0704</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VAZQUEZ GARCIA</t>
+          <t>A. ARTERO CARA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.3724</v>
+        <v>3.8159</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8995</v>
+        <v>4.7206</v>
       </c>
       <c r="F17" t="n">
-        <v>2.4728</v>
+        <v>-0.9046999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3248</v>
+        <v>3.0807</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.0143</v>
+        <v>0.184</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3391</v>
+        <v>2.8967</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3558</v>
+        <v>3.3912</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1147</v>
+        <v>1.0492</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2411</v>
+        <v>2.342</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.031</v>
+        <v>-0.3105</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.129</v>
+        <v>-0.8652</v>
       </c>
       <c r="O17" t="n">
-        <v>1.098</v>
+        <v>0.5547</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9911</v>
+        <v>1.1893</v>
       </c>
       <c r="S17" t="n">
-        <v>4.576</v>
+        <v>0.4864</v>
       </c>
       <c r="T17" t="n">
-        <v>2.4597</v>
+        <v>1.0628</v>
       </c>
       <c r="U17" t="n">
-        <v>2.1163</v>
+        <v>-0.5764</v>
       </c>
       <c r="V17" t="n">
-        <v>0.4627</v>
+        <v>-0.9405</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0663</v>
+        <v>0.2666</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6036</v>
+        <v>-1.2071</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. ARTERO CARA</t>
+          <t>O. DIAZ GUILLEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3876</v>
+        <v>1.9017</v>
       </c>
       <c r="E18" t="n">
-        <v>4.5169</v>
+        <v>1.1103</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1293</v>
+        <v>0.7913</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0807</v>
+        <v>2.2518</v>
       </c>
       <c r="H18" t="n">
-        <v>0.184</v>
+        <v>0.2849</v>
       </c>
       <c r="I18" t="n">
-        <v>2.8967</v>
+        <v>1.9669</v>
       </c>
       <c r="J18" t="n">
-        <v>3.3912</v>
+        <v>2.8222</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0492</v>
+        <v>1.6817</v>
       </c>
       <c r="L18" t="n">
-        <v>2.342</v>
+        <v>1.1405</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3105</v>
+        <v>-0.5704</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8652</v>
+        <v>-1.3967</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5547</v>
+        <v>0.8264</v>
       </c>
       <c r="P18" t="n">
-        <v>1.1893</v>
+        <v>-1.1893</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1893</v>
+        <v>0.7929</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0581</v>
+        <v>0.5726</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8591</v>
+        <v>0.0038</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.801</v>
+        <v>0.5688</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.9405</v>
+        <v>0.2666</v>
       </c>
       <c r="W18" t="n">
         <v>0.2666</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.2071</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. CRIADO SALVADOR</t>
+          <t>A. VAZQUEZ GARCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2454</v>
+        <v>1.584</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5177</v>
+        <v>0.0659</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2723</v>
+        <v>1.5182</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.265</v>
+        <v>0.3248</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.4965</v>
+        <v>-1.0143</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2315</v>
+        <v>1.3391</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.7488</v>
+        <v>0.3558</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.8331</v>
+        <v>0.1147</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0842</v>
+        <v>0.2411</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.5162</v>
+        <v>-0.031</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6634</v>
+        <v>-1.129</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1472</v>
+        <v>1.098</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1893</v>
+        <v>-0.9911</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.9822</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1893</v>
+        <v>0.9911</v>
       </c>
       <c r="S19" t="n">
-        <v>1.2507</v>
+        <v>1.7876</v>
       </c>
       <c r="T19" t="n">
-        <v>1.663</v>
+        <v>0.626</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4123</v>
+        <v>1.1616</v>
       </c>
       <c r="V19" t="n">
-        <v>0.0704</v>
+        <v>0.4627</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6036</v>
+        <v>1.0663</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5331</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>O. DIAZ GUILLEN</t>
+          <t>J. CRIADO SALVADOR</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0867</v>
+        <v>1.1364</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2954</v>
+        <v>1.2121</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7913</v>
+        <v>-0.0757</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2518</v>
+        <v>-1.265</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2849</v>
+        <v>-1.4965</v>
       </c>
       <c r="I20" t="n">
-        <v>1.9669</v>
+        <v>0.2315</v>
       </c>
       <c r="J20" t="n">
-        <v>2.8222</v>
+        <v>-0.7488</v>
       </c>
       <c r="K20" t="n">
-        <v>1.6817</v>
+        <v>-0.8331</v>
       </c>
       <c r="L20" t="n">
-        <v>1.1405</v>
+        <v>0.0842</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5704</v>
+        <v>-0.5162</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3967</v>
+        <v>-0.6634</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8264</v>
+        <v>0.1472</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1893</v>
+        <v>1.1893</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9822</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7929</v>
+        <v>1.1893</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2423</v>
+        <v>1.1417</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8112</v>
+        <v>1.3574</v>
       </c>
       <c r="U20" t="n">
-        <v>0.5688</v>
+        <v>-0.2157</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2666</v>
+        <v>0.0704</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2666</v>
+        <v>0.6036</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.5331</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.285</v>
+        <v>-2.7548</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.6057</v>
+        <v>-3.3001</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3207</v>
+        <v>0.5453</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8792</v>
@@ -2092,13 +2092,13 @@
         <v>1.5858</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.276</v>
+        <v>0.2542</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4847</v>
+        <v>0.7903</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.7607</v>
+        <v>-0.5361</v>
       </c>
       <c r="V21" t="n">
         <v>0.2666</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2956</v>
+        <v>-2.9129</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6108</v>
+        <v>-1.509</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6848</v>
+        <v>-1.404</v>
       </c>
       <c r="G22" t="n">
         <v>-1.499</v>
@@ -2170,13 +2170,13 @@
         <v>0.3964</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.312</v>
+        <v>0.0707</v>
       </c>
       <c r="T22" t="n">
-        <v>0.18</v>
+        <v>0.2818</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4919</v>
+        <v>-0.2112</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8811</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0713</v>
+        <v>-3.1232</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.1616</v>
+        <v>-2.5504</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.9097</v>
+        <v>-0.5728</v>
       </c>
       <c r="G23" t="n">
         <v>-2.9525</v>
@@ -2248,13 +2248,13 @@
         <v>0.5947</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7224</v>
+        <v>0.2258</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8112</v>
+        <v>-0.1999</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0888</v>
+        <v>0.4257</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.4154</v>
+        <v>-3.6886</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3078</v>
+        <v>-4.0022</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1076</v>
+        <v>0.3136</v>
       </c>
       <c r="G24" t="n">
         <v>-0.5878</v>
@@ -2326,13 +2326,13 @@
         <v>0.7929</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.1229</v>
+        <v>0.6039</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.132</v>
+        <v>0.1736</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0091</v>
+        <v>0.4303</v>
       </c>
       <c r="V24" t="n">
         <v>-0.5331</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.3996</v>
+        <v>14.3995</v>
       </c>
       <c r="E25" t="n">
-        <v>9.231299999999997</v>
+        <v>9.231199999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>5.1683</v>
+        <v>5.1682</v>
       </c>
       <c r="G25" t="n">
         <v>7.668399999999998</v>
@@ -2383,7 +2383,7 @@
         <v>8.283000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.110600000000001</v>
+        <v>3.1106</v>
       </c>
       <c r="M25" t="n">
         <v>-3.7253</v>
@@ -2392,7 +2392,7 @@
         <v>-11.9888</v>
       </c>
       <c r="O25" t="n">
-        <v>8.2637</v>
+        <v>8.263699999999998</v>
       </c>
       <c r="P25" t="n">
         <v>-2.9733</v>
@@ -2410,10 +2410,10 @@
         <v>5.7829</v>
       </c>
       <c r="U25" t="n">
-        <v>3.1923</v>
+        <v>3.1921</v>
       </c>
       <c r="V25" t="n">
-        <v>0.7292999999999995</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="W25" t="n">
         <v>4.9392</v>
